--- a/tests/abiotic/settings.xlsx
+++ b/tests/abiotic/settings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05286D34-FFD7-4B66-8FED-D3652D5F2A65}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{960FF344-EA37-4640-B818-E83E34AB37F3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,17 +130,16 @@
     <t>constant_species</t>
   </si>
   <si>
-    <t>CO2, M</t>
-  </si>
-  <si>
     <t>SO4:gd(j), S8:2.62d-4</t>
   </si>
   <si>
     <t>H2S : 3.85d9/1d5/11d0, SO2 : 10d0*3.85d9/1d5/11d0, CO : 3d9/1d5, H2 : 1d10/1d5, NH3 : 5.3d9/1d5</t>
   </si>
   <si>
-    <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1, CHOCHO:0.3</t>
+  </si>
+  <si>
+    <t>CO2, M,H2O</t>
   </si>
 </sst>
 </file>
@@ -151,7 +150,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -164,7 +163,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -227,6 +226,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -547,14 +550,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8537C3E-DE4A-A54B-9562-BA16146EEF99}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -565,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,7 +579,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -587,7 +590,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -598,7 +601,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -609,7 +612,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -620,7 +623,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -631,7 +634,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -642,7 +645,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -653,7 +656,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -664,7 +667,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -675,7 +678,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -686,7 +689,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -694,10 +697,10 @@
         <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -705,10 +708,10 @@
         <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -716,10 +719,10 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -727,7 +730,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/tests/abiotic/settings.xlsx
+++ b/tests/abiotic/settings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{960FF344-EA37-4640-B818-E83E34AB37F3}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D4BB508-2443-4D64-B059-826069CA81F8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
   </bookViews>
@@ -139,7 +139,7 @@
     <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1, CHOCHO:0.3</t>
   </si>
   <si>
-    <t>CO2, M,H2O</t>
+    <t>CO2, M, H2O</t>
   </si>
 </sst>
 </file>

--- a/tests/abiotic/settings.xlsx
+++ b/tests/abiotic/settings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D4BB508-2443-4D64-B059-826069CA81F8}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{158195A9-E951-4F22-83BA-120E244FDAF3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
   </bookViews>
@@ -139,7 +139,7 @@
     <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1, CHOCHO:0.3</t>
   </si>
   <si>
-    <t>CO2, M, H2O</t>
+    <t>CO2, M</t>
   </si>
 </sst>
 </file>
@@ -226,10 +226,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/tests/abiotic/settings.xlsx
+++ b/tests/abiotic/settings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{158195A9-E951-4F22-83BA-120E244FDAF3}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3C13756-57D8-4D7E-8B95-7FB9DD8927BC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
   </bookViews>
@@ -139,7 +139,7 @@
     <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1, CHOCHO:0.3</t>
   </si>
   <si>
-    <t>CO2, M</t>
+    <t>CO2, M, H2O</t>
   </si>
 </sst>
 </file>
@@ -226,6 +226,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/tests/abiotic/settings.xlsx
+++ b/tests/abiotic/settings.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3C13756-57D8-4D7E-8B95-7FB9DD8927BC}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{998C4554-0EEB-44C7-9D28-8A194EFC1369}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -136,10 +136,10 @@
     <t>H2S : 3.85d9/1d5/11d0, SO2 : 10d0*3.85d9/1d5/11d0, CO : 3d9/1d5, H2 : 1d10/1d5, NH3 : 5.3d9/1d5</t>
   </si>
   <si>
-    <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1, CHOCHO:0.3</t>
-  </si>
-  <si>
     <t>CO2, M, H2O</t>
+  </si>
+  <si>
+    <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1, CHOCHO:0.08</t>
   </si>
 </sst>
 </file>
@@ -226,10 +226,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -708,7 +704,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -719,7 +715,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">

--- a/tests/abiotic/settings.xlsx
+++ b/tests/abiotic/settings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{998C4554-0EEB-44C7-9D28-8A194EFC1369}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4183933-6A40-4DCB-9D2A-8BA64261F72F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
+    <workbookView xWindow="10" yWindow="1270" windowWidth="14790" windowHeight="7430" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -139,7 +139,7 @@
     <t>CO2, M, H2O</t>
   </si>
   <si>
-    <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1, CHOCHO:0.08</t>
+    <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1, CHOCHO:0.3</t>
   </si>
 </sst>
 </file>
@@ -226,6 +226,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/tests/abiotic/settings.xlsx
+++ b/tests/abiotic/settings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4183933-6A40-4DCB-9D2A-8BA64261F72F}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E861BC2E-8689-4C12-85C5-50031326C6E0}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="1270" windowWidth="14790" windowHeight="7430" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -139,7 +139,8 @@
     <t>CO2, M, H2O</t>
   </si>
   <si>
-    <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1, CHOCHO:0.3</t>
+    <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.2, HO2:1, CH2O:0.1, HCO:1, OH:1, O:1, H:1, CO:0.1, CH3:0.1, HCN:0.1, CHOCHO:0.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -150,7 +151,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -163,7 +164,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -226,10 +227,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,14 +547,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8537C3E-DE4A-A54B-9562-BA16146EEF99}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -568,7 +565,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +576,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -590,7 +587,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -601,7 +598,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -612,7 +609,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -623,7 +620,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -634,7 +631,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -645,7 +642,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -656,7 +653,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -667,7 +664,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -678,7 +675,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -689,7 +686,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -700,7 +697,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -711,7 +708,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -722,7 +719,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
